--- a/bnc-streamlit-app/data/playerlist.xlsx
+++ b/bnc-streamlit-app/data/playerlist.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wt_an\WT Analysis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wt_an\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8B649F3-0181-4AB5-ABB1-9AEA40A69337}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5DC23F5-D034-4AC3-B648-368CB564FC91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F99C2274-98D2-4399-9250-8E7A0D0DACF8}"/>
   </bookViews>
@@ -545,9 +545,6 @@
     <t>S. Mané</t>
   </si>
   <si>
-    <t>2wk1549tkz80oet8226euj7jp</t>
-  </si>
-  <si>
     <t>Y. Tielemans</t>
   </si>
   <si>
@@ -915,6 +912,9 @@
   </si>
   <si>
     <t>BnC Position</t>
+  </si>
+  <si>
+    <t>cotiiu6mjkfx5xa63nhfbdf4l</t>
   </si>
 </sst>
 </file>
@@ -1306,7 +1306,7 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -1317,10 +1317,10 @@
         <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D2" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -1331,10 +1331,10 @@
         <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -1345,10 +1345,10 @@
         <v>8</v>
       </c>
       <c r="C4" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D4" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -1359,10 +1359,10 @@
         <v>10</v>
       </c>
       <c r="C5" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D5" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1373,10 +1373,10 @@
         <v>12</v>
       </c>
       <c r="C6" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D6" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -1387,10 +1387,10 @@
         <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D7" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -1401,10 +1401,10 @@
         <v>16</v>
       </c>
       <c r="C8" t="s">
+        <v>263</v>
+      </c>
+      <c r="D8" t="s">
         <v>264</v>
-      </c>
-      <c r="D8" t="s">
-        <v>265</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -1415,10 +1415,10 @@
         <v>18</v>
       </c>
       <c r="C9" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D9" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -1429,10 +1429,10 @@
         <v>20</v>
       </c>
       <c r="C10" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D10" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -1443,10 +1443,10 @@
         <v>22</v>
       </c>
       <c r="C11" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D11" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -1457,10 +1457,10 @@
         <v>24</v>
       </c>
       <c r="C12" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D12" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -1471,10 +1471,10 @@
         <v>26</v>
       </c>
       <c r="C13" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D13" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -1485,10 +1485,10 @@
         <v>28</v>
       </c>
       <c r="C14" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D14" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -1499,10 +1499,10 @@
         <v>30</v>
       </c>
       <c r="C15" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D15" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -1513,10 +1513,10 @@
         <v>32</v>
       </c>
       <c r="C16" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D16" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -1527,10 +1527,10 @@
         <v>34</v>
       </c>
       <c r="C17" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D17" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -1541,10 +1541,10 @@
         <v>36</v>
       </c>
       <c r="C18" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D18" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -1555,10 +1555,10 @@
         <v>38</v>
       </c>
       <c r="C19" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D19" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -1569,10 +1569,10 @@
         <v>40</v>
       </c>
       <c r="C20" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D20" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -1583,10 +1583,10 @@
         <v>42</v>
       </c>
       <c r="C21" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D21" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -1597,10 +1597,10 @@
         <v>44</v>
       </c>
       <c r="C22" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D22" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -1611,10 +1611,10 @@
         <v>46</v>
       </c>
       <c r="C23" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D23" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -1625,10 +1625,10 @@
         <v>48</v>
       </c>
       <c r="C24" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D24" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1639,10 +1639,10 @@
         <v>50</v>
       </c>
       <c r="C25" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D25" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -1653,10 +1653,10 @@
         <v>52</v>
       </c>
       <c r="C26" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -1667,10 +1667,10 @@
         <v>54</v>
       </c>
       <c r="C27" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D27" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -1681,10 +1681,10 @@
         <v>56</v>
       </c>
       <c r="C28" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D28" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -1695,10 +1695,10 @@
         <v>58</v>
       </c>
       <c r="C29" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D29" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -1709,10 +1709,10 @@
         <v>60</v>
       </c>
       <c r="C30" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D30" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -1723,10 +1723,10 @@
         <v>62</v>
       </c>
       <c r="C31" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -1737,10 +1737,10 @@
         <v>64</v>
       </c>
       <c r="C32" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D32" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -1751,10 +1751,10 @@
         <v>66</v>
       </c>
       <c r="C33" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D33" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -1765,10 +1765,10 @@
         <v>68</v>
       </c>
       <c r="C34" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D34" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -1779,10 +1779,10 @@
         <v>70</v>
       </c>
       <c r="C35" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D35" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -1793,10 +1793,10 @@
         <v>72</v>
       </c>
       <c r="C36" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D36" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -1807,10 +1807,10 @@
         <v>74</v>
       </c>
       <c r="C37" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D37" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -1821,10 +1821,10 @@
         <v>76</v>
       </c>
       <c r="C38" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D38" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -1835,10 +1835,10 @@
         <v>78</v>
       </c>
       <c r="C39" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D39" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -1849,10 +1849,10 @@
         <v>80</v>
       </c>
       <c r="C40" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D40" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -1863,10 +1863,10 @@
         <v>82</v>
       </c>
       <c r="C41" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D41" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -1877,10 +1877,10 @@
         <v>84</v>
       </c>
       <c r="C42" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D42" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -1891,10 +1891,10 @@
         <v>86</v>
       </c>
       <c r="C43" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D43" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -1905,10 +1905,10 @@
         <v>88</v>
       </c>
       <c r="C44" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D44" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
@@ -1919,10 +1919,10 @@
         <v>90</v>
       </c>
       <c r="C45" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D45" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -1933,10 +1933,10 @@
         <v>92</v>
       </c>
       <c r="C46" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D46" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -1947,10 +1947,10 @@
         <v>94</v>
       </c>
       <c r="C47" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D47" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -1961,10 +1961,10 @@
         <v>96</v>
       </c>
       <c r="C48" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
@@ -1975,10 +1975,10 @@
         <v>98</v>
       </c>
       <c r="C49" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D49" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
@@ -1989,10 +1989,10 @@
         <v>100</v>
       </c>
       <c r="C50" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
@@ -2003,10 +2003,10 @@
         <v>102</v>
       </c>
       <c r="C51" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D51" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
@@ -2017,10 +2017,10 @@
         <v>104</v>
       </c>
       <c r="C52" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D52" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
@@ -2031,10 +2031,10 @@
         <v>106</v>
       </c>
       <c r="C53" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
@@ -2045,10 +2045,10 @@
         <v>108</v>
       </c>
       <c r="C54" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D54" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
@@ -2059,10 +2059,10 @@
         <v>110</v>
       </c>
       <c r="C55" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D55" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
@@ -2073,10 +2073,10 @@
         <v>112</v>
       </c>
       <c r="C56" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D56" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
@@ -2087,10 +2087,10 @@
         <v>114</v>
       </c>
       <c r="C57" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D57" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
@@ -2101,10 +2101,10 @@
         <v>116</v>
       </c>
       <c r="C58" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D58" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
@@ -2115,10 +2115,10 @@
         <v>118</v>
       </c>
       <c r="C59" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D59" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
@@ -2129,10 +2129,10 @@
         <v>120</v>
       </c>
       <c r="C60" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D60" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
@@ -2143,10 +2143,10 @@
         <v>122</v>
       </c>
       <c r="C61" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D61" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
@@ -2157,10 +2157,10 @@
         <v>124</v>
       </c>
       <c r="C62" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D62" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
@@ -2171,10 +2171,10 @@
         <v>126</v>
       </c>
       <c r="C63" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D63" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
@@ -2185,10 +2185,10 @@
         <v>128</v>
       </c>
       <c r="C64" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
@@ -2199,10 +2199,10 @@
         <v>130</v>
       </c>
       <c r="C65" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D65" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
@@ -2213,10 +2213,10 @@
         <v>132</v>
       </c>
       <c r="C66" t="s">
+        <v>263</v>
+      </c>
+      <c r="D66" t="s">
         <v>264</v>
-      </c>
-      <c r="D66" t="s">
-        <v>265</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
@@ -2227,10 +2227,10 @@
         <v>134</v>
       </c>
       <c r="C67" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D67" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
@@ -2241,10 +2241,10 @@
         <v>136</v>
       </c>
       <c r="C68" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D68" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
@@ -2255,10 +2255,10 @@
         <v>138</v>
       </c>
       <c r="C69" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D69" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
@@ -2269,10 +2269,10 @@
         <v>140</v>
       </c>
       <c r="C70" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="D70" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
@@ -2283,10 +2283,10 @@
         <v>142</v>
       </c>
       <c r="C71" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D71" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
@@ -2297,10 +2297,10 @@
         <v>144</v>
       </c>
       <c r="C72" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D72" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
@@ -2311,10 +2311,10 @@
         <v>146</v>
       </c>
       <c r="C73" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D73" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
@@ -2325,10 +2325,10 @@
         <v>148</v>
       </c>
       <c r="C74" t="s">
+        <v>263</v>
+      </c>
+      <c r="D74" t="s">
         <v>264</v>
-      </c>
-      <c r="D74" t="s">
-        <v>265</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
@@ -2339,10 +2339,10 @@
         <v>150</v>
       </c>
       <c r="C75" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D75" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
@@ -2353,10 +2353,10 @@
         <v>152</v>
       </c>
       <c r="C76" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D76" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
@@ -2367,10 +2367,10 @@
         <v>154</v>
       </c>
       <c r="C77" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D77" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
@@ -2381,10 +2381,10 @@
         <v>156</v>
       </c>
       <c r="C78" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D78" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
@@ -2395,10 +2395,10 @@
         <v>158</v>
       </c>
       <c r="C79" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D79" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
@@ -2409,10 +2409,10 @@
         <v>160</v>
       </c>
       <c r="C80" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D80" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
@@ -2423,10 +2423,10 @@
         <v>162</v>
       </c>
       <c r="C81" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D81" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
@@ -2437,10 +2437,10 @@
         <v>164</v>
       </c>
       <c r="C82" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.25">
@@ -2451,10 +2451,10 @@
         <v>166</v>
       </c>
       <c r="C83" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D83" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.25">
@@ -2462,771 +2462,771 @@
         <v>167</v>
       </c>
       <c r="B84" t="s">
-        <v>168</v>
+        <v>291</v>
       </c>
       <c r="C84" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D84" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
+        <v>168</v>
+      </c>
+      <c r="B85" t="s">
         <v>169</v>
       </c>
-      <c r="B85" t="s">
-        <v>170</v>
-      </c>
       <c r="C85" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D85" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
+        <v>170</v>
+      </c>
+      <c r="B86" t="s">
         <v>171</v>
       </c>
-      <c r="B86" t="s">
-        <v>172</v>
-      </c>
       <c r="C86" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D86" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
+        <v>172</v>
+      </c>
+      <c r="B87" t="s">
         <v>173</v>
       </c>
-      <c r="B87" t="s">
-        <v>174</v>
-      </c>
       <c r="C87" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D87" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
+        <v>174</v>
+      </c>
+      <c r="B88" t="s">
         <v>175</v>
       </c>
-      <c r="B88" t="s">
-        <v>176</v>
-      </c>
       <c r="C88" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D88" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
+        <v>176</v>
+      </c>
+      <c r="B89" t="s">
         <v>177</v>
       </c>
-      <c r="B89" t="s">
-        <v>178</v>
-      </c>
       <c r="C89" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D89" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
+        <v>178</v>
+      </c>
+      <c r="B90" t="s">
         <v>179</v>
       </c>
-      <c r="B90" t="s">
-        <v>180</v>
-      </c>
       <c r="C90" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D90" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
+        <v>180</v>
+      </c>
+      <c r="B91" t="s">
         <v>181</v>
       </c>
-      <c r="B91" t="s">
-        <v>182</v>
-      </c>
       <c r="C91" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D91" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
+        <v>182</v>
+      </c>
+      <c r="B92" t="s">
         <v>183</v>
       </c>
-      <c r="B92" t="s">
-        <v>184</v>
-      </c>
       <c r="C92" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D92" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
+        <v>184</v>
+      </c>
+      <c r="B93" t="s">
         <v>185</v>
       </c>
-      <c r="B93" t="s">
-        <v>186</v>
-      </c>
       <c r="C93" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D93" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
+        <v>186</v>
+      </c>
+      <c r="B94" t="s">
         <v>187</v>
       </c>
-      <c r="B94" t="s">
-        <v>188</v>
-      </c>
       <c r="C94" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D94" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
+        <v>188</v>
+      </c>
+      <c r="B95" t="s">
         <v>189</v>
       </c>
-      <c r="B95" t="s">
-        <v>190</v>
-      </c>
       <c r="C95" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D95" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
+        <v>190</v>
+      </c>
+      <c r="B96" t="s">
         <v>191</v>
       </c>
-      <c r="B96" t="s">
-        <v>192</v>
-      </c>
       <c r="C96" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D96" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
+        <v>192</v>
+      </c>
+      <c r="B97" t="s">
         <v>193</v>
       </c>
-      <c r="B97" t="s">
-        <v>194</v>
-      </c>
       <c r="C97" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D97" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
+        <v>194</v>
+      </c>
+      <c r="B98" t="s">
         <v>195</v>
       </c>
-      <c r="B98" t="s">
-        <v>196</v>
-      </c>
       <c r="C98" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D98" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
+        <v>196</v>
+      </c>
+      <c r="B99" t="s">
         <v>197</v>
       </c>
-      <c r="B99" t="s">
-        <v>198</v>
-      </c>
       <c r="C99" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D99" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
+        <v>198</v>
+      </c>
+      <c r="B100" t="s">
         <v>199</v>
       </c>
-      <c r="B100" t="s">
-        <v>200</v>
-      </c>
       <c r="C100" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D100" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
+        <v>200</v>
+      </c>
+      <c r="B101" t="s">
         <v>201</v>
       </c>
-      <c r="B101" t="s">
-        <v>202</v>
-      </c>
       <c r="C101" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D101" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
+        <v>202</v>
+      </c>
+      <c r="B102" t="s">
         <v>203</v>
       </c>
-      <c r="B102" t="s">
-        <v>204</v>
-      </c>
       <c r="C102" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D102" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
+        <v>204</v>
+      </c>
+      <c r="B103" t="s">
         <v>205</v>
       </c>
-      <c r="B103" t="s">
-        <v>206</v>
-      </c>
       <c r="C103" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D103" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
+        <v>206</v>
+      </c>
+      <c r="B104" t="s">
         <v>207</v>
       </c>
-      <c r="B104" t="s">
-        <v>208</v>
-      </c>
       <c r="C104" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D104" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
+        <v>208</v>
+      </c>
+      <c r="B105" t="s">
         <v>209</v>
       </c>
-      <c r="B105" t="s">
-        <v>210</v>
-      </c>
       <c r="C105" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D105" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
+        <v>210</v>
+      </c>
+      <c r="B106" t="s">
         <v>211</v>
       </c>
-      <c r="B106" t="s">
-        <v>212</v>
-      </c>
       <c r="C106" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D106" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
+        <v>212</v>
+      </c>
+      <c r="B107" t="s">
         <v>213</v>
       </c>
-      <c r="B107" t="s">
-        <v>214</v>
-      </c>
       <c r="C107" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D107" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
+        <v>214</v>
+      </c>
+      <c r="B108" t="s">
         <v>215</v>
       </c>
-      <c r="B108" t="s">
-        <v>216</v>
-      </c>
       <c r="C108" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D108" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
+        <v>216</v>
+      </c>
+      <c r="B109" t="s">
         <v>217</v>
       </c>
-      <c r="B109" t="s">
-        <v>218</v>
-      </c>
       <c r="C109" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D109" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
+        <v>218</v>
+      </c>
+      <c r="B110" t="s">
         <v>219</v>
       </c>
-      <c r="B110" t="s">
-        <v>220</v>
-      </c>
       <c r="C110" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D110" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
+        <v>220</v>
+      </c>
+      <c r="B111" t="s">
         <v>221</v>
       </c>
-      <c r="B111" t="s">
-        <v>222</v>
-      </c>
       <c r="C111" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D111" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
+        <v>222</v>
+      </c>
+      <c r="B112" t="s">
         <v>223</v>
       </c>
-      <c r="B112" t="s">
-        <v>224</v>
-      </c>
       <c r="C112" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D112" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
+        <v>224</v>
+      </c>
+      <c r="B113" t="s">
         <v>225</v>
       </c>
-      <c r="B113" t="s">
-        <v>226</v>
-      </c>
       <c r="C113" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D113" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
+        <v>226</v>
+      </c>
+      <c r="B114" t="s">
         <v>227</v>
       </c>
-      <c r="B114" t="s">
-        <v>228</v>
-      </c>
       <c r="C114" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D114" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
+        <v>228</v>
+      </c>
+      <c r="B115" t="s">
         <v>229</v>
       </c>
-      <c r="B115" t="s">
-        <v>230</v>
-      </c>
       <c r="C115" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D115" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
+        <v>230</v>
+      </c>
+      <c r="B116" t="s">
         <v>231</v>
       </c>
-      <c r="B116" t="s">
-        <v>232</v>
-      </c>
       <c r="C116" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D116" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
+        <v>232</v>
+      </c>
+      <c r="B117" t="s">
         <v>233</v>
       </c>
-      <c r="B117" t="s">
-        <v>234</v>
-      </c>
       <c r="C117" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D117" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
+        <v>234</v>
+      </c>
+      <c r="B118" t="s">
         <v>235</v>
       </c>
-      <c r="B118" t="s">
-        <v>236</v>
-      </c>
       <c r="C118" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D118" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
+        <v>236</v>
+      </c>
+      <c r="B119" t="s">
         <v>237</v>
       </c>
-      <c r="B119" t="s">
-        <v>238</v>
-      </c>
       <c r="C119" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D119" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
+        <v>238</v>
+      </c>
+      <c r="B120" t="s">
         <v>239</v>
       </c>
-      <c r="B120" t="s">
-        <v>240</v>
-      </c>
       <c r="C120" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D120" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
+        <v>240</v>
+      </c>
+      <c r="B121" t="s">
         <v>241</v>
       </c>
-      <c r="B121" t="s">
-        <v>242</v>
-      </c>
       <c r="C121" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D121" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
+        <v>242</v>
+      </c>
+      <c r="B122" t="s">
         <v>243</v>
       </c>
-      <c r="B122" t="s">
-        <v>244</v>
-      </c>
       <c r="C122" t="s">
+        <v>271</v>
+      </c>
+      <c r="D122" t="s">
         <v>272</v>
-      </c>
-      <c r="D122" t="s">
-        <v>273</v>
       </c>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
+        <v>244</v>
+      </c>
+      <c r="B123" t="s">
         <v>245</v>
       </c>
-      <c r="B123" t="s">
-        <v>246</v>
-      </c>
       <c r="C123" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D123" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
+        <v>246</v>
+      </c>
+      <c r="B124" t="s">
         <v>247</v>
       </c>
-      <c r="B124" t="s">
-        <v>248</v>
-      </c>
       <c r="C124" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D124" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
+        <v>248</v>
+      </c>
+      <c r="B125" t="s">
         <v>249</v>
       </c>
-      <c r="B125" t="s">
-        <v>250</v>
-      </c>
       <c r="C125" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="D125" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
+        <v>250</v>
+      </c>
+      <c r="B126" t="s">
         <v>251</v>
       </c>
-      <c r="B126" t="s">
-        <v>252</v>
-      </c>
       <c r="C126" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D126" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
+        <v>252</v>
+      </c>
+      <c r="B127" t="s">
         <v>253</v>
       </c>
-      <c r="B127" t="s">
-        <v>254</v>
-      </c>
       <c r="C127" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D127" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
+        <v>254</v>
+      </c>
+      <c r="B128" t="s">
         <v>255</v>
       </c>
-      <c r="B128" t="s">
-        <v>256</v>
-      </c>
       <c r="C128" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D128" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
+        <v>256</v>
+      </c>
+      <c r="B129" t="s">
         <v>257</v>
       </c>
-      <c r="B129" t="s">
-        <v>258</v>
-      </c>
       <c r="C129" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D129" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C130" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D130" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C131" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D131" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C132" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D132" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C133" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D133" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C134" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D134" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C135" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D135" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C136" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D136" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C137" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D137" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C138" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D138" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C139" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D139" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C140" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D140" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C141" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D141" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C142" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D142" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C143" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D143" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C144" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D144" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="145" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C145" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D145" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
   </sheetData>

--- a/bnc-streamlit-app/data/playerlist.xlsx
+++ b/bnc-streamlit-app/data/playerlist.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wt_an\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wt_an\WT Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5DC23F5-D034-4AC3-B648-368CB564FC91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4FFAA81-39FE-4394-9C44-EFBA155209FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F99C2274-98D2-4399-9250-8E7A0D0DACF8}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="548" uniqueCount="292">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="564" uniqueCount="308">
   <si>
     <t>Player</t>
   </si>
@@ -545,6 +545,9 @@
     <t>S. Mané</t>
   </si>
   <si>
+    <t>2wk1549tkz80oet8226euj7jp</t>
+  </si>
+  <si>
     <t>Y. Tielemans</t>
   </si>
   <si>
@@ -914,7 +917,52 @@
     <t>BnC Position</t>
   </si>
   <si>
-    <t>cotiiu6mjkfx5xa63nhfbdf4l</t>
+    <t>F. Nmecha</t>
+  </si>
+  <si>
+    <t>6384gzzxuxs6pvmrn8qx4d7u1</t>
+  </si>
+  <si>
+    <t>N. Brown</t>
+  </si>
+  <si>
+    <t>cr4e64yry1ttwcjxh2klb4ui2</t>
+  </si>
+  <si>
+    <t>J. Manzambi</t>
+  </si>
+  <si>
+    <t>6g4cnzr3dh0veul5svzkhmxw4</t>
+  </si>
+  <si>
+    <t>S. Dest</t>
+  </si>
+  <si>
+    <t>b0me6l44boibnwpbtasxoy02x</t>
+  </si>
+  <si>
+    <t>B. Brobbey</t>
+  </si>
+  <si>
+    <t>9c2i7ddl2uh7kuhwq62klkyui</t>
+  </si>
+  <si>
+    <t>R. De Paul</t>
+  </si>
+  <si>
+    <t>3ga7qj3h3dbmqucxmaxhmrjdh</t>
+  </si>
+  <si>
+    <t>R. Vargas</t>
+  </si>
+  <si>
+    <t>4zrut521fzw9fddqt74pnl756</t>
+  </si>
+  <si>
+    <t>F. Medina</t>
+  </si>
+  <si>
+    <t>br7zigajqee6fms35zhm1sb8p</t>
   </si>
 </sst>
 </file>
@@ -1306,7 +1354,7 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -1317,10 +1365,10 @@
         <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -1331,10 +1379,10 @@
         <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -1345,10 +1393,10 @@
         <v>8</v>
       </c>
       <c r="C4" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -1359,10 +1407,10 @@
         <v>10</v>
       </c>
       <c r="C5" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D5" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1373,10 +1421,10 @@
         <v>12</v>
       </c>
       <c r="C6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -1387,10 +1435,10 @@
         <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D7" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -1401,10 +1449,10 @@
         <v>16</v>
       </c>
       <c r="C8" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D8" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -1415,10 +1463,10 @@
         <v>18</v>
       </c>
       <c r="C9" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D9" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -1429,10 +1477,10 @@
         <v>20</v>
       </c>
       <c r="C10" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D10" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -1443,10 +1491,10 @@
         <v>22</v>
       </c>
       <c r="C11" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D11" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -1457,10 +1505,10 @@
         <v>24</v>
       </c>
       <c r="C12" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D12" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -1471,10 +1519,10 @@
         <v>26</v>
       </c>
       <c r="C13" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D13" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -1485,10 +1533,10 @@
         <v>28</v>
       </c>
       <c r="C14" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D14" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -1499,10 +1547,10 @@
         <v>30</v>
       </c>
       <c r="C15" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D15" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -1513,10 +1561,10 @@
         <v>32</v>
       </c>
       <c r="C16" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D16" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -1527,10 +1575,10 @@
         <v>34</v>
       </c>
       <c r="C17" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -1541,10 +1589,10 @@
         <v>36</v>
       </c>
       <c r="C18" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D18" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -1555,10 +1603,10 @@
         <v>38</v>
       </c>
       <c r="C19" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D19" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -1569,10 +1617,10 @@
         <v>40</v>
       </c>
       <c r="C20" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D20" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -1583,10 +1631,10 @@
         <v>42</v>
       </c>
       <c r="C21" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D21" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -1597,10 +1645,10 @@
         <v>44</v>
       </c>
       <c r="C22" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D22" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -1611,10 +1659,10 @@
         <v>46</v>
       </c>
       <c r="C23" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D23" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -1625,10 +1673,10 @@
         <v>48</v>
       </c>
       <c r="C24" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D24" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1639,10 +1687,10 @@
         <v>50</v>
       </c>
       <c r="C25" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D25" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -1653,10 +1701,10 @@
         <v>52</v>
       </c>
       <c r="C26" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D26" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -1667,10 +1715,10 @@
         <v>54</v>
       </c>
       <c r="C27" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D27" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -1681,10 +1729,10 @@
         <v>56</v>
       </c>
       <c r="C28" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -1695,10 +1743,10 @@
         <v>58</v>
       </c>
       <c r="C29" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D29" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -1709,10 +1757,10 @@
         <v>60</v>
       </c>
       <c r="C30" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D30" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -1723,10 +1771,10 @@
         <v>62</v>
       </c>
       <c r="C31" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D31" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -1737,10 +1785,10 @@
         <v>64</v>
       </c>
       <c r="C32" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D32" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -1751,10 +1799,10 @@
         <v>66</v>
       </c>
       <c r="C33" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D33" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -1765,10 +1813,10 @@
         <v>68</v>
       </c>
       <c r="C34" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -1779,10 +1827,10 @@
         <v>70</v>
       </c>
       <c r="C35" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D35" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -1793,10 +1841,10 @@
         <v>72</v>
       </c>
       <c r="C36" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D36" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -1807,10 +1855,10 @@
         <v>74</v>
       </c>
       <c r="C37" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D37" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -1821,10 +1869,10 @@
         <v>76</v>
       </c>
       <c r="C38" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D38" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -1835,10 +1883,10 @@
         <v>78</v>
       </c>
       <c r="C39" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D39" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -1849,10 +1897,10 @@
         <v>80</v>
       </c>
       <c r="C40" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D40" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -1863,10 +1911,10 @@
         <v>82</v>
       </c>
       <c r="C41" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D41" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -1877,10 +1925,10 @@
         <v>84</v>
       </c>
       <c r="C42" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D42" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -1891,10 +1939,10 @@
         <v>86</v>
       </c>
       <c r="C43" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D43" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -1905,10 +1953,10 @@
         <v>88</v>
       </c>
       <c r="C44" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D44" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
@@ -1919,10 +1967,10 @@
         <v>90</v>
       </c>
       <c r="C45" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D45" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -1933,10 +1981,10 @@
         <v>92</v>
       </c>
       <c r="C46" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D46" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -1947,10 +1995,10 @@
         <v>94</v>
       </c>
       <c r="C47" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D47" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -1961,10 +2009,10 @@
         <v>96</v>
       </c>
       <c r="C48" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D48" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
@@ -1975,10 +2023,10 @@
         <v>98</v>
       </c>
       <c r="C49" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D49" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
@@ -1989,10 +2037,10 @@
         <v>100</v>
       </c>
       <c r="C50" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D50" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
@@ -2003,10 +2051,10 @@
         <v>102</v>
       </c>
       <c r="C51" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
@@ -2017,10 +2065,10 @@
         <v>104</v>
       </c>
       <c r="C52" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D52" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
@@ -2031,10 +2079,10 @@
         <v>106</v>
       </c>
       <c r="C53" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D53" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
@@ -2045,10 +2093,10 @@
         <v>108</v>
       </c>
       <c r="C54" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D54" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
@@ -2059,10 +2107,10 @@
         <v>110</v>
       </c>
       <c r="C55" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D55" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
@@ -2073,10 +2121,10 @@
         <v>112</v>
       </c>
       <c r="C56" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D56" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
@@ -2087,10 +2135,10 @@
         <v>114</v>
       </c>
       <c r="C57" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D57" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
@@ -2101,10 +2149,10 @@
         <v>116</v>
       </c>
       <c r="C58" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D58" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
@@ -2115,10 +2163,10 @@
         <v>118</v>
       </c>
       <c r="C59" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
@@ -2129,10 +2177,10 @@
         <v>120</v>
       </c>
       <c r="C60" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D60" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
@@ -2143,10 +2191,10 @@
         <v>122</v>
       </c>
       <c r="C61" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D61" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
@@ -2157,10 +2205,10 @@
         <v>124</v>
       </c>
       <c r="C62" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D62" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
@@ -2171,10 +2219,10 @@
         <v>126</v>
       </c>
       <c r="C63" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D63" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
@@ -2185,10 +2233,10 @@
         <v>128</v>
       </c>
       <c r="C64" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D64" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
@@ -2199,10 +2247,10 @@
         <v>130</v>
       </c>
       <c r="C65" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D65" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
@@ -2213,10 +2261,10 @@
         <v>132</v>
       </c>
       <c r="C66" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D66" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
@@ -2227,10 +2275,10 @@
         <v>134</v>
       </c>
       <c r="C67" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D67" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
@@ -2241,10 +2289,10 @@
         <v>136</v>
       </c>
       <c r="C68" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D68" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
@@ -2255,10 +2303,10 @@
         <v>138</v>
       </c>
       <c r="C69" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D69" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
@@ -2269,10 +2317,10 @@
         <v>140</v>
       </c>
       <c r="C70" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D70" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
@@ -2283,10 +2331,10 @@
         <v>142</v>
       </c>
       <c r="C71" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D71" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
@@ -2297,10 +2345,10 @@
         <v>144</v>
       </c>
       <c r="C72" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D72" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
@@ -2311,10 +2359,10 @@
         <v>146</v>
       </c>
       <c r="C73" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
@@ -2325,10 +2373,10 @@
         <v>148</v>
       </c>
       <c r="C74" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D74" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
@@ -2339,10 +2387,10 @@
         <v>150</v>
       </c>
       <c r="C75" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D75" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
@@ -2353,10 +2401,10 @@
         <v>152</v>
       </c>
       <c r="C76" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D76" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
@@ -2367,10 +2415,10 @@
         <v>154</v>
       </c>
       <c r="C77" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D77" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
@@ -2381,10 +2429,10 @@
         <v>156</v>
       </c>
       <c r="C78" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D78" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
@@ -2395,10 +2443,10 @@
         <v>158</v>
       </c>
       <c r="C79" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D79" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
@@ -2409,10 +2457,10 @@
         <v>160</v>
       </c>
       <c r="C80" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D80" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
@@ -2423,10 +2471,10 @@
         <v>162</v>
       </c>
       <c r="C81" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="D81" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
@@ -2437,10 +2485,10 @@
         <v>164</v>
       </c>
       <c r="C82" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D82" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.25">
@@ -2451,10 +2499,10 @@
         <v>166</v>
       </c>
       <c r="C83" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.25">
@@ -2462,771 +2510,819 @@
         <v>167</v>
       </c>
       <c r="B84" t="s">
-        <v>291</v>
+        <v>168</v>
       </c>
       <c r="C84" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D84" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B85" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C85" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D85" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B86" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C86" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D86" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B87" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C87" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D87" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B88" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C88" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D88" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B89" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C89" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D89" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B90" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C90" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D90" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B91" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C91" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D91" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B92" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C92" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D92" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B93" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C93" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D93" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B94" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C94" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D94" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B95" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C95" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B96" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C96" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D96" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B97" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C97" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D97" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B98" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C98" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="D98" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B99" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C99" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D99" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B100" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C100" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D100" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B101" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C101" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B102" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C102" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D102" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B103" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C103" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D103" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B104" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C104" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D104" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B105" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C105" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D105" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B106" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C106" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D106" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B107" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C107" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D107" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B108" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C108" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D108" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B109" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C109" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D109" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B110" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C110" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D110" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B111" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C111" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D111" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B112" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C112" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D112" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B113" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C113" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D113" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B114" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C114" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D114" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B115" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C115" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D115" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B116" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C116" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D116" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B117" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C117" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D117" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B118" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C118" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D118" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B119" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C119" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D119" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B120" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C120" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D120" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B121" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C121" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B122" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C122" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D122" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B123" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C123" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D123" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B124" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C124" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D124" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B125" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C125" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D125" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B126" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C126" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D126" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B127" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C127" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D127" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B128" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C128" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D128" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B129" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C129" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D129" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>292</v>
+      </c>
+      <c r="B130" t="s">
+        <v>293</v>
+      </c>
       <c r="C130" t="s">
-        <v>289</v>
+        <v>266</v>
       </c>
       <c r="D130" t="s">
-        <v>289</v>
+        <v>265</v>
       </c>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>294</v>
+      </c>
+      <c r="B131" t="s">
+        <v>295</v>
+      </c>
       <c r="C131" t="s">
-        <v>289</v>
+        <v>266</v>
       </c>
       <c r="D131" t="s">
-        <v>289</v>
+        <v>270</v>
       </c>
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>296</v>
+      </c>
+      <c r="B132" t="s">
+        <v>297</v>
+      </c>
       <c r="C132" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="D132" t="s">
-        <v>289</v>
+        <v>265</v>
       </c>
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>298</v>
+      </c>
+      <c r="B133" t="s">
+        <v>299</v>
+      </c>
       <c r="C133" t="s">
-        <v>289</v>
+        <v>276</v>
       </c>
       <c r="D133" t="s">
-        <v>289</v>
+        <v>270</v>
       </c>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>300</v>
+      </c>
+      <c r="B134" t="s">
+        <v>301</v>
+      </c>
       <c r="C134" t="s">
-        <v>289</v>
+        <v>275</v>
       </c>
       <c r="D134" t="s">
-        <v>289</v>
+        <v>260</v>
       </c>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>302</v>
+      </c>
+      <c r="B135" t="s">
+        <v>303</v>
+      </c>
       <c r="C135" t="s">
-        <v>289</v>
+        <v>263</v>
       </c>
       <c r="D135" t="s">
-        <v>289</v>
+        <v>265</v>
       </c>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>304</v>
+      </c>
+      <c r="B136" t="s">
+        <v>305</v>
+      </c>
       <c r="C136" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="D136" t="s">
-        <v>289</v>
+        <v>265</v>
       </c>
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>306</v>
+      </c>
+      <c r="B137" t="s">
+        <v>307</v>
+      </c>
       <c r="C137" t="s">
-        <v>289</v>
+        <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>289</v>
+        <v>270</v>
       </c>
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C138" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D138" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C139" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D139" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C140" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D140" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C141" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D141" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C142" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D142" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C143" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D143" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C144" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D144" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="145" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C145" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D145" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
   </sheetData>

--- a/bnc-streamlit-app/data/playerlist.xlsx
+++ b/bnc-streamlit-app/data/playerlist.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wt_an\WT Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4FFAA81-39FE-4394-9C44-EFBA155209FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A11D18F-3119-487B-A153-72F8BFB9584F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F99C2274-98D2-4399-9250-8E7A0D0DACF8}"/>
   </bookViews>
@@ -545,9 +545,6 @@
     <t>S. Mané</t>
   </si>
   <si>
-    <t>2wk1549tkz80oet8226euj7jp</t>
-  </si>
-  <si>
     <t>Y. Tielemans</t>
   </si>
   <si>
@@ -963,6 +960,9 @@
   </si>
   <si>
     <t>br7zigajqee6fms35zhm1sb8p</t>
+  </si>
+  <si>
+    <t>cotiiu6mjkfx5xa63nhfbdf4l</t>
   </si>
 </sst>
 </file>
@@ -1354,7 +1354,7 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -1365,10 +1365,10 @@
         <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D2" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -1379,10 +1379,10 @@
         <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -1393,10 +1393,10 @@
         <v>8</v>
       </c>
       <c r="C4" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D4" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -1407,10 +1407,10 @@
         <v>10</v>
       </c>
       <c r="C5" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D5" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1421,10 +1421,10 @@
         <v>12</v>
       </c>
       <c r="C6" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D6" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -1435,10 +1435,10 @@
         <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D7" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -1449,10 +1449,10 @@
         <v>16</v>
       </c>
       <c r="C8" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D8" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -1463,10 +1463,10 @@
         <v>18</v>
       </c>
       <c r="C9" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D9" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -1477,10 +1477,10 @@
         <v>20</v>
       </c>
       <c r="C10" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D10" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -1491,10 +1491,10 @@
         <v>22</v>
       </c>
       <c r="C11" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D11" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -1505,10 +1505,10 @@
         <v>24</v>
       </c>
       <c r="C12" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D12" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -1519,10 +1519,10 @@
         <v>26</v>
       </c>
       <c r="C13" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D13" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -1533,10 +1533,10 @@
         <v>28</v>
       </c>
       <c r="C14" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D14" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -1547,10 +1547,10 @@
         <v>30</v>
       </c>
       <c r="C15" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D15" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -1561,10 +1561,10 @@
         <v>32</v>
       </c>
       <c r="C16" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D16" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -1575,10 +1575,10 @@
         <v>34</v>
       </c>
       <c r="C17" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D17" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -1589,10 +1589,10 @@
         <v>36</v>
       </c>
       <c r="C18" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D18" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -1603,10 +1603,10 @@
         <v>38</v>
       </c>
       <c r="C19" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D19" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -1617,10 +1617,10 @@
         <v>40</v>
       </c>
       <c r="C20" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D20" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -1631,10 +1631,10 @@
         <v>42</v>
       </c>
       <c r="C21" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D21" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -1645,10 +1645,10 @@
         <v>44</v>
       </c>
       <c r="C22" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D22" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -1659,10 +1659,10 @@
         <v>46</v>
       </c>
       <c r="C23" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D23" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -1673,10 +1673,10 @@
         <v>48</v>
       </c>
       <c r="C24" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D24" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1687,10 +1687,10 @@
         <v>50</v>
       </c>
       <c r="C25" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D25" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -1701,10 +1701,10 @@
         <v>52</v>
       </c>
       <c r="C26" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -1715,10 +1715,10 @@
         <v>54</v>
       </c>
       <c r="C27" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D27" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -1729,10 +1729,10 @@
         <v>56</v>
       </c>
       <c r="C28" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D28" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -1743,10 +1743,10 @@
         <v>58</v>
       </c>
       <c r="C29" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D29" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -1757,10 +1757,10 @@
         <v>60</v>
       </c>
       <c r="C30" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D30" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -1771,10 +1771,10 @@
         <v>62</v>
       </c>
       <c r="C31" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -1785,10 +1785,10 @@
         <v>64</v>
       </c>
       <c r="C32" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D32" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -1799,10 +1799,10 @@
         <v>66</v>
       </c>
       <c r="C33" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D33" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -1813,10 +1813,10 @@
         <v>68</v>
       </c>
       <c r="C34" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D34" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -1827,10 +1827,10 @@
         <v>70</v>
       </c>
       <c r="C35" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D35" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -1841,10 +1841,10 @@
         <v>72</v>
       </c>
       <c r="C36" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D36" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -1855,10 +1855,10 @@
         <v>74</v>
       </c>
       <c r="C37" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D37" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -1869,10 +1869,10 @@
         <v>76</v>
       </c>
       <c r="C38" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D38" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -1883,10 +1883,10 @@
         <v>78</v>
       </c>
       <c r="C39" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D39" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -1897,10 +1897,10 @@
         <v>80</v>
       </c>
       <c r="C40" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D40" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -1911,10 +1911,10 @@
         <v>82</v>
       </c>
       <c r="C41" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D41" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -1925,10 +1925,10 @@
         <v>84</v>
       </c>
       <c r="C42" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D42" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -1939,10 +1939,10 @@
         <v>86</v>
       </c>
       <c r="C43" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D43" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -1953,10 +1953,10 @@
         <v>88</v>
       </c>
       <c r="C44" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D44" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
@@ -1967,10 +1967,10 @@
         <v>90</v>
       </c>
       <c r="C45" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D45" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -1981,10 +1981,10 @@
         <v>92</v>
       </c>
       <c r="C46" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D46" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -1995,10 +1995,10 @@
         <v>94</v>
       </c>
       <c r="C47" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D47" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -2009,10 +2009,10 @@
         <v>96</v>
       </c>
       <c r="C48" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
@@ -2023,10 +2023,10 @@
         <v>98</v>
       </c>
       <c r="C49" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D49" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
@@ -2037,10 +2037,10 @@
         <v>100</v>
       </c>
       <c r="C50" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
@@ -2051,10 +2051,10 @@
         <v>102</v>
       </c>
       <c r="C51" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D51" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
@@ -2065,10 +2065,10 @@
         <v>104</v>
       </c>
       <c r="C52" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D52" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
@@ -2079,10 +2079,10 @@
         <v>106</v>
       </c>
       <c r="C53" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
@@ -2093,10 +2093,10 @@
         <v>108</v>
       </c>
       <c r="C54" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D54" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
@@ -2107,10 +2107,10 @@
         <v>110</v>
       </c>
       <c r="C55" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D55" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
@@ -2121,10 +2121,10 @@
         <v>112</v>
       </c>
       <c r="C56" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D56" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
@@ -2135,10 +2135,10 @@
         <v>114</v>
       </c>
       <c r="C57" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D57" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
@@ -2149,10 +2149,10 @@
         <v>116</v>
       </c>
       <c r="C58" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D58" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
@@ -2163,10 +2163,10 @@
         <v>118</v>
       </c>
       <c r="C59" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D59" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
@@ -2177,10 +2177,10 @@
         <v>120</v>
       </c>
       <c r="C60" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D60" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
@@ -2191,10 +2191,10 @@
         <v>122</v>
       </c>
       <c r="C61" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D61" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
@@ -2205,10 +2205,10 @@
         <v>124</v>
       </c>
       <c r="C62" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D62" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
@@ -2219,10 +2219,10 @@
         <v>126</v>
       </c>
       <c r="C63" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D63" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
@@ -2233,10 +2233,10 @@
         <v>128</v>
       </c>
       <c r="C64" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
@@ -2247,10 +2247,10 @@
         <v>130</v>
       </c>
       <c r="C65" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D65" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
@@ -2261,10 +2261,10 @@
         <v>132</v>
       </c>
       <c r="C66" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
@@ -2275,10 +2275,10 @@
         <v>134</v>
       </c>
       <c r="C67" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D67" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
@@ -2289,10 +2289,10 @@
         <v>136</v>
       </c>
       <c r="C68" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D68" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
@@ -2303,10 +2303,10 @@
         <v>138</v>
       </c>
       <c r="C69" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D69" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
@@ -2317,10 +2317,10 @@
         <v>140</v>
       </c>
       <c r="C70" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="D70" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
@@ -2331,10 +2331,10 @@
         <v>142</v>
       </c>
       <c r="C71" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D71" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
@@ -2345,10 +2345,10 @@
         <v>144</v>
       </c>
       <c r="C72" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D72" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
@@ -2359,10 +2359,10 @@
         <v>146</v>
       </c>
       <c r="C73" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D73" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
@@ -2373,10 +2373,10 @@
         <v>148</v>
       </c>
       <c r="C74" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
@@ -2387,10 +2387,10 @@
         <v>150</v>
       </c>
       <c r="C75" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D75" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
@@ -2401,10 +2401,10 @@
         <v>152</v>
       </c>
       <c r="C76" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D76" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
@@ -2415,10 +2415,10 @@
         <v>154</v>
       </c>
       <c r="C77" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D77" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
@@ -2429,10 +2429,10 @@
         <v>156</v>
       </c>
       <c r="C78" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D78" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
@@ -2443,10 +2443,10 @@
         <v>158</v>
       </c>
       <c r="C79" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D79" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
@@ -2457,10 +2457,10 @@
         <v>160</v>
       </c>
       <c r="C80" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D80" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
@@ -2471,10 +2471,10 @@
         <v>162</v>
       </c>
       <c r="C81" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D81" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
@@ -2485,10 +2485,10 @@
         <v>164</v>
       </c>
       <c r="C82" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.25">
@@ -2499,10 +2499,10 @@
         <v>166</v>
       </c>
       <c r="C83" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D83" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.25">
@@ -2510,819 +2510,819 @@
         <v>167</v>
       </c>
       <c r="B84" t="s">
-        <v>168</v>
+        <v>307</v>
       </c>
       <c r="C84" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D84" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
+        <v>168</v>
+      </c>
+      <c r="B85" t="s">
         <v>169</v>
       </c>
-      <c r="B85" t="s">
-        <v>170</v>
-      </c>
       <c r="C85" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D85" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
+        <v>170</v>
+      </c>
+      <c r="B86" t="s">
         <v>171</v>
       </c>
-      <c r="B86" t="s">
-        <v>172</v>
-      </c>
       <c r="C86" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D86" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
+        <v>172</v>
+      </c>
+      <c r="B87" t="s">
         <v>173</v>
       </c>
-      <c r="B87" t="s">
-        <v>174</v>
-      </c>
       <c r="C87" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D87" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
+        <v>174</v>
+      </c>
+      <c r="B88" t="s">
         <v>175</v>
       </c>
-      <c r="B88" t="s">
-        <v>176</v>
-      </c>
       <c r="C88" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D88" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
+        <v>176</v>
+      </c>
+      <c r="B89" t="s">
         <v>177</v>
       </c>
-      <c r="B89" t="s">
-        <v>178</v>
-      </c>
       <c r="C89" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D89" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
+        <v>178</v>
+      </c>
+      <c r="B90" t="s">
         <v>179</v>
       </c>
-      <c r="B90" t="s">
-        <v>180</v>
-      </c>
       <c r="C90" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D90" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
+        <v>180</v>
+      </c>
+      <c r="B91" t="s">
         <v>181</v>
       </c>
-      <c r="B91" t="s">
-        <v>182</v>
-      </c>
       <c r="C91" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D91" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
+        <v>182</v>
+      </c>
+      <c r="B92" t="s">
         <v>183</v>
       </c>
-      <c r="B92" t="s">
-        <v>184</v>
-      </c>
       <c r="C92" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D92" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
+        <v>184</v>
+      </c>
+      <c r="B93" t="s">
         <v>185</v>
       </c>
-      <c r="B93" t="s">
-        <v>186</v>
-      </c>
       <c r="C93" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D93" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
+        <v>186</v>
+      </c>
+      <c r="B94" t="s">
         <v>187</v>
       </c>
-      <c r="B94" t="s">
-        <v>188</v>
-      </c>
       <c r="C94" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D94" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
+        <v>188</v>
+      </c>
+      <c r="B95" t="s">
         <v>189</v>
       </c>
-      <c r="B95" t="s">
-        <v>190</v>
-      </c>
       <c r="C95" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D95" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
+        <v>190</v>
+      </c>
+      <c r="B96" t="s">
         <v>191</v>
       </c>
-      <c r="B96" t="s">
-        <v>192</v>
-      </c>
       <c r="C96" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D96" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
+        <v>192</v>
+      </c>
+      <c r="B97" t="s">
         <v>193</v>
       </c>
-      <c r="B97" t="s">
-        <v>194</v>
-      </c>
       <c r="C97" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D97" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
+        <v>194</v>
+      </c>
+      <c r="B98" t="s">
         <v>195</v>
       </c>
-      <c r="B98" t="s">
-        <v>196</v>
-      </c>
       <c r="C98" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D98" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
+        <v>196</v>
+      </c>
+      <c r="B99" t="s">
         <v>197</v>
       </c>
-      <c r="B99" t="s">
-        <v>198</v>
-      </c>
       <c r="C99" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D99" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
+        <v>198</v>
+      </c>
+      <c r="B100" t="s">
         <v>199</v>
       </c>
-      <c r="B100" t="s">
-        <v>200</v>
-      </c>
       <c r="C100" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D100" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
+        <v>200</v>
+      </c>
+      <c r="B101" t="s">
         <v>201</v>
       </c>
-      <c r="B101" t="s">
-        <v>202</v>
-      </c>
       <c r="C101" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D101" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
+        <v>202</v>
+      </c>
+      <c r="B102" t="s">
         <v>203</v>
       </c>
-      <c r="B102" t="s">
-        <v>204</v>
-      </c>
       <c r="C102" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D102" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
+        <v>204</v>
+      </c>
+      <c r="B103" t="s">
         <v>205</v>
       </c>
-      <c r="B103" t="s">
-        <v>206</v>
-      </c>
       <c r="C103" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D103" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
+        <v>206</v>
+      </c>
+      <c r="B104" t="s">
         <v>207</v>
       </c>
-      <c r="B104" t="s">
-        <v>208</v>
-      </c>
       <c r="C104" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D104" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
+        <v>208</v>
+      </c>
+      <c r="B105" t="s">
         <v>209</v>
       </c>
-      <c r="B105" t="s">
-        <v>210</v>
-      </c>
       <c r="C105" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D105" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
+        <v>210</v>
+      </c>
+      <c r="B106" t="s">
         <v>211</v>
       </c>
-      <c r="B106" t="s">
-        <v>212</v>
-      </c>
       <c r="C106" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D106" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
+        <v>212</v>
+      </c>
+      <c r="B107" t="s">
         <v>213</v>
       </c>
-      <c r="B107" t="s">
-        <v>214</v>
-      </c>
       <c r="C107" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D107" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
+        <v>214</v>
+      </c>
+      <c r="B108" t="s">
         <v>215</v>
       </c>
-      <c r="B108" t="s">
-        <v>216</v>
-      </c>
       <c r="C108" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D108" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
+        <v>216</v>
+      </c>
+      <c r="B109" t="s">
         <v>217</v>
       </c>
-      <c r="B109" t="s">
-        <v>218</v>
-      </c>
       <c r="C109" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D109" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
+        <v>218</v>
+      </c>
+      <c r="B110" t="s">
         <v>219</v>
       </c>
-      <c r="B110" t="s">
-        <v>220</v>
-      </c>
       <c r="C110" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D110" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
+        <v>220</v>
+      </c>
+      <c r="B111" t="s">
         <v>221</v>
       </c>
-      <c r="B111" t="s">
-        <v>222</v>
-      </c>
       <c r="C111" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D111" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
+        <v>222</v>
+      </c>
+      <c r="B112" t="s">
         <v>223</v>
       </c>
-      <c r="B112" t="s">
-        <v>224</v>
-      </c>
       <c r="C112" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D112" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
+        <v>224</v>
+      </c>
+      <c r="B113" t="s">
         <v>225</v>
       </c>
-      <c r="B113" t="s">
-        <v>226</v>
-      </c>
       <c r="C113" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D113" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
+        <v>226</v>
+      </c>
+      <c r="B114" t="s">
         <v>227</v>
       </c>
-      <c r="B114" t="s">
-        <v>228</v>
-      </c>
       <c r="C114" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D114" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
+        <v>228</v>
+      </c>
+      <c r="B115" t="s">
         <v>229</v>
       </c>
-      <c r="B115" t="s">
-        <v>230</v>
-      </c>
       <c r="C115" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D115" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
+        <v>230</v>
+      </c>
+      <c r="B116" t="s">
         <v>231</v>
       </c>
-      <c r="B116" t="s">
-        <v>232</v>
-      </c>
       <c r="C116" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D116" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
+        <v>232</v>
+      </c>
+      <c r="B117" t="s">
         <v>233</v>
       </c>
-      <c r="B117" t="s">
-        <v>234</v>
-      </c>
       <c r="C117" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D117" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
+        <v>234</v>
+      </c>
+      <c r="B118" t="s">
         <v>235</v>
       </c>
-      <c r="B118" t="s">
-        <v>236</v>
-      </c>
       <c r="C118" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D118" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
+        <v>236</v>
+      </c>
+      <c r="B119" t="s">
         <v>237</v>
       </c>
-      <c r="B119" t="s">
-        <v>238</v>
-      </c>
       <c r="C119" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D119" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
+        <v>238</v>
+      </c>
+      <c r="B120" t="s">
         <v>239</v>
       </c>
-      <c r="B120" t="s">
-        <v>240</v>
-      </c>
       <c r="C120" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D120" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
+        <v>240</v>
+      </c>
+      <c r="B121" t="s">
         <v>241</v>
       </c>
-      <c r="B121" t="s">
-        <v>242</v>
-      </c>
       <c r="C121" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D121" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
+        <v>242</v>
+      </c>
+      <c r="B122" t="s">
         <v>243</v>
       </c>
-      <c r="B122" t="s">
-        <v>244</v>
-      </c>
       <c r="C122" t="s">
+        <v>271</v>
+      </c>
+      <c r="D122" t="s">
         <v>272</v>
-      </c>
-      <c r="D122" t="s">
-        <v>273</v>
       </c>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
+        <v>244</v>
+      </c>
+      <c r="B123" t="s">
         <v>245</v>
       </c>
-      <c r="B123" t="s">
-        <v>246</v>
-      </c>
       <c r="C123" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D123" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
+        <v>246</v>
+      </c>
+      <c r="B124" t="s">
         <v>247</v>
       </c>
-      <c r="B124" t="s">
-        <v>248</v>
-      </c>
       <c r="C124" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D124" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
+        <v>248</v>
+      </c>
+      <c r="B125" t="s">
         <v>249</v>
       </c>
-      <c r="B125" t="s">
-        <v>250</v>
-      </c>
       <c r="C125" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="D125" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
+        <v>250</v>
+      </c>
+      <c r="B126" t="s">
         <v>251</v>
       </c>
-      <c r="B126" t="s">
-        <v>252</v>
-      </c>
       <c r="C126" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D126" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
+        <v>252</v>
+      </c>
+      <c r="B127" t="s">
         <v>253</v>
       </c>
-      <c r="B127" t="s">
-        <v>254</v>
-      </c>
       <c r="C127" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D127" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
+        <v>254</v>
+      </c>
+      <c r="B128" t="s">
         <v>255</v>
       </c>
-      <c r="B128" t="s">
-        <v>256</v>
-      </c>
       <c r="C128" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D128" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
+        <v>256</v>
+      </c>
+      <c r="B129" t="s">
         <v>257</v>
       </c>
-      <c r="B129" t="s">
-        <v>258</v>
-      </c>
       <c r="C129" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D129" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
+        <v>291</v>
+      </c>
+      <c r="B130" t="s">
         <v>292</v>
       </c>
-      <c r="B130" t="s">
-        <v>293</v>
-      </c>
       <c r="C130" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D130" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
+        <v>293</v>
+      </c>
+      <c r="B131" t="s">
         <v>294</v>
       </c>
-      <c r="B131" t="s">
-        <v>295</v>
-      </c>
       <c r="C131" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D131" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
+        <v>295</v>
+      </c>
+      <c r="B132" t="s">
         <v>296</v>
       </c>
-      <c r="B132" t="s">
-        <v>297</v>
-      </c>
       <c r="C132" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D132" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
+        <v>297</v>
+      </c>
+      <c r="B133" t="s">
         <v>298</v>
       </c>
-      <c r="B133" t="s">
-        <v>299</v>
-      </c>
       <c r="C133" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D133" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
+        <v>299</v>
+      </c>
+      <c r="B134" t="s">
         <v>300</v>
       </c>
-      <c r="B134" t="s">
-        <v>301</v>
-      </c>
       <c r="C134" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D134" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
+        <v>301</v>
+      </c>
+      <c r="B135" t="s">
         <v>302</v>
       </c>
-      <c r="B135" t="s">
-        <v>303</v>
-      </c>
       <c r="C135" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D135" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
+        <v>303</v>
+      </c>
+      <c r="B136" t="s">
         <v>304</v>
       </c>
-      <c r="B136" t="s">
-        <v>305</v>
-      </c>
       <c r="C136" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D136" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
+        <v>305</v>
+      </c>
+      <c r="B137" t="s">
         <v>306</v>
       </c>
-      <c r="B137" t="s">
-        <v>307</v>
-      </c>
       <c r="C137" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D137" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C138" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D138" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C139" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D139" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C140" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D140" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C141" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D141" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C142" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D142" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C143" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D143" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C144" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D144" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="145" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C145" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D145" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
   </sheetData>

--- a/bnc-streamlit-app/data/playerlist.xlsx
+++ b/bnc-streamlit-app/data/playerlist.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wt_an\WT Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A11D18F-3119-487B-A153-72F8BFB9584F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3290730C-F02D-48E3-9960-72C2D6FB4115}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F99C2274-98D2-4399-9250-8E7A0D0DACF8}"/>
   </bookViews>
@@ -596,9 +596,6 @@
     <t>M. van de Ven</t>
   </si>
   <si>
-    <t>aqlakf0mo95rlktf6xdbaegh5</t>
-  </si>
-  <si>
     <t>Diogo Costa</t>
   </si>
   <si>
@@ -963,6 +960,9 @@
   </si>
   <si>
     <t>cotiiu6mjkfx5xa63nhfbdf4l</t>
+  </si>
+  <si>
+    <t>dodddfi0l5i36vlgbaybhzeqy</t>
   </si>
 </sst>
 </file>
@@ -1354,7 +1354,7 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -1365,10 +1365,10 @@
         <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D2" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -1379,10 +1379,10 @@
         <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D3" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -1393,10 +1393,10 @@
         <v>8</v>
       </c>
       <c r="C4" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D4" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -1407,10 +1407,10 @@
         <v>10</v>
       </c>
       <c r="C5" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1421,10 +1421,10 @@
         <v>12</v>
       </c>
       <c r="C6" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D6" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -1435,10 +1435,10 @@
         <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D7" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -1449,10 +1449,10 @@
         <v>16</v>
       </c>
       <c r="C8" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D8" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -1463,10 +1463,10 @@
         <v>18</v>
       </c>
       <c r="C9" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D9" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -1477,10 +1477,10 @@
         <v>20</v>
       </c>
       <c r="C10" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D10" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -1491,10 +1491,10 @@
         <v>22</v>
       </c>
       <c r="C11" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D11" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -1505,10 +1505,10 @@
         <v>24</v>
       </c>
       <c r="C12" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D12" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -1519,10 +1519,10 @@
         <v>26</v>
       </c>
       <c r="C13" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D13" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -1533,10 +1533,10 @@
         <v>28</v>
       </c>
       <c r="C14" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D14" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -1547,10 +1547,10 @@
         <v>30</v>
       </c>
       <c r="C15" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D15" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -1561,10 +1561,10 @@
         <v>32</v>
       </c>
       <c r="C16" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D16" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -1575,10 +1575,10 @@
         <v>34</v>
       </c>
       <c r="C17" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D17" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -1589,10 +1589,10 @@
         <v>36</v>
       </c>
       <c r="C18" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D18" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -1603,10 +1603,10 @@
         <v>38</v>
       </c>
       <c r="C19" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D19" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -1617,10 +1617,10 @@
         <v>40</v>
       </c>
       <c r="C20" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D20" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -1631,10 +1631,10 @@
         <v>42</v>
       </c>
       <c r="C21" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D21" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -1645,10 +1645,10 @@
         <v>44</v>
       </c>
       <c r="C22" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D22" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -1659,10 +1659,10 @@
         <v>46</v>
       </c>
       <c r="C23" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D23" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -1673,10 +1673,10 @@
         <v>48</v>
       </c>
       <c r="C24" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D24" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1687,10 +1687,10 @@
         <v>50</v>
       </c>
       <c r="C25" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D25" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -1701,10 +1701,10 @@
         <v>52</v>
       </c>
       <c r="C26" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D26" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -1715,10 +1715,10 @@
         <v>54</v>
       </c>
       <c r="C27" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D27" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -1729,10 +1729,10 @@
         <v>56</v>
       </c>
       <c r="C28" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D28" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -1743,10 +1743,10 @@
         <v>58</v>
       </c>
       <c r="C29" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D29" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -1757,10 +1757,10 @@
         <v>60</v>
       </c>
       <c r="C30" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D30" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -1771,10 +1771,10 @@
         <v>62</v>
       </c>
       <c r="C31" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D31" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -1785,10 +1785,10 @@
         <v>64</v>
       </c>
       <c r="C32" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D32" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -1799,10 +1799,10 @@
         <v>66</v>
       </c>
       <c r="C33" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D33" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -1813,10 +1813,10 @@
         <v>68</v>
       </c>
       <c r="C34" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D34" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -1827,10 +1827,10 @@
         <v>70</v>
       </c>
       <c r="C35" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D35" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -1841,10 +1841,10 @@
         <v>72</v>
       </c>
       <c r="C36" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -1855,10 +1855,10 @@
         <v>74</v>
       </c>
       <c r="C37" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D37" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -1869,10 +1869,10 @@
         <v>76</v>
       </c>
       <c r="C38" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D38" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -1883,10 +1883,10 @@
         <v>78</v>
       </c>
       <c r="C39" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D39" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -1897,10 +1897,10 @@
         <v>80</v>
       </c>
       <c r="C40" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D40" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -1911,10 +1911,10 @@
         <v>82</v>
       </c>
       <c r="C41" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D41" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -1925,10 +1925,10 @@
         <v>84</v>
       </c>
       <c r="C42" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D42" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -1939,10 +1939,10 @@
         <v>86</v>
       </c>
       <c r="C43" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D43" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -1953,10 +1953,10 @@
         <v>88</v>
       </c>
       <c r="C44" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
@@ -1967,10 +1967,10 @@
         <v>90</v>
       </c>
       <c r="C45" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D45" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -1981,10 +1981,10 @@
         <v>92</v>
       </c>
       <c r="C46" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D46" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -1995,10 +1995,10 @@
         <v>94</v>
       </c>
       <c r="C47" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D47" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -2009,10 +2009,10 @@
         <v>96</v>
       </c>
       <c r="C48" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D48" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
@@ -2023,10 +2023,10 @@
         <v>98</v>
       </c>
       <c r="C49" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D49" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
@@ -2037,10 +2037,10 @@
         <v>100</v>
       </c>
       <c r="C50" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D50" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
@@ -2051,10 +2051,10 @@
         <v>102</v>
       </c>
       <c r="C51" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D51" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
@@ -2065,10 +2065,10 @@
         <v>104</v>
       </c>
       <c r="C52" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D52" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
@@ -2079,10 +2079,10 @@
         <v>106</v>
       </c>
       <c r="C53" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D53" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
@@ -2093,10 +2093,10 @@
         <v>108</v>
       </c>
       <c r="C54" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D54" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
@@ -2107,10 +2107,10 @@
         <v>110</v>
       </c>
       <c r="C55" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D55" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
@@ -2121,10 +2121,10 @@
         <v>112</v>
       </c>
       <c r="C56" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D56" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
@@ -2135,10 +2135,10 @@
         <v>114</v>
       </c>
       <c r="C57" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D57" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
@@ -2149,10 +2149,10 @@
         <v>116</v>
       </c>
       <c r="C58" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D58" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
@@ -2163,10 +2163,10 @@
         <v>118</v>
       </c>
       <c r="C59" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D59" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
@@ -2177,10 +2177,10 @@
         <v>120</v>
       </c>
       <c r="C60" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D60" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
@@ -2191,10 +2191,10 @@
         <v>122</v>
       </c>
       <c r="C61" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D61" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
@@ -2205,10 +2205,10 @@
         <v>124</v>
       </c>
       <c r="C62" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D62" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
@@ -2219,10 +2219,10 @@
         <v>126</v>
       </c>
       <c r="C63" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D63" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
@@ -2233,10 +2233,10 @@
         <v>128</v>
       </c>
       <c r="C64" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D64" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
@@ -2247,10 +2247,10 @@
         <v>130</v>
       </c>
       <c r="C65" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D65" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
@@ -2261,10 +2261,10 @@
         <v>132</v>
       </c>
       <c r="C66" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D66" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
@@ -2275,10 +2275,10 @@
         <v>134</v>
       </c>
       <c r="C67" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D67" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
@@ -2289,10 +2289,10 @@
         <v>136</v>
       </c>
       <c r="C68" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D68" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
@@ -2303,10 +2303,10 @@
         <v>138</v>
       </c>
       <c r="C69" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D69" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
@@ -2317,10 +2317,10 @@
         <v>140</v>
       </c>
       <c r="C70" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D70" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
@@ -2331,10 +2331,10 @@
         <v>142</v>
       </c>
       <c r="C71" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D71" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
@@ -2345,10 +2345,10 @@
         <v>144</v>
       </c>
       <c r="C72" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D72" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
@@ -2359,10 +2359,10 @@
         <v>146</v>
       </c>
       <c r="C73" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D73" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
@@ -2373,10 +2373,10 @@
         <v>148</v>
       </c>
       <c r="C74" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D74" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
@@ -2387,10 +2387,10 @@
         <v>150</v>
       </c>
       <c r="C75" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D75" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
@@ -2401,10 +2401,10 @@
         <v>152</v>
       </c>
       <c r="C76" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D76" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
@@ -2415,10 +2415,10 @@
         <v>154</v>
       </c>
       <c r="C77" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D77" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
@@ -2429,10 +2429,10 @@
         <v>156</v>
       </c>
       <c r="C78" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="D78" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
@@ -2443,10 +2443,10 @@
         <v>158</v>
       </c>
       <c r="C79" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D79" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
@@ -2457,10 +2457,10 @@
         <v>160</v>
       </c>
       <c r="C80" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D80" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
@@ -2471,10 +2471,10 @@
         <v>162</v>
       </c>
       <c r="C81" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D81" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
@@ -2485,10 +2485,10 @@
         <v>164</v>
       </c>
       <c r="C82" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D82" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.25">
@@ -2499,10 +2499,10 @@
         <v>166</v>
       </c>
       <c r="C83" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D83" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.25">
@@ -2510,13 +2510,13 @@
         <v>167</v>
       </c>
       <c r="B84" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C84" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D84" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.25">
@@ -2527,10 +2527,10 @@
         <v>169</v>
       </c>
       <c r="C85" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D85" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.25">
@@ -2541,10 +2541,10 @@
         <v>171</v>
       </c>
       <c r="C86" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D86" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.25">
@@ -2555,10 +2555,10 @@
         <v>173</v>
       </c>
       <c r="C87" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D87" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.25">
@@ -2569,10 +2569,10 @@
         <v>175</v>
       </c>
       <c r="C88" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D88" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.25">
@@ -2583,10 +2583,10 @@
         <v>177</v>
       </c>
       <c r="C89" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D89" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.25">
@@ -2597,10 +2597,10 @@
         <v>179</v>
       </c>
       <c r="C90" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D90" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.25">
@@ -2611,10 +2611,10 @@
         <v>181</v>
       </c>
       <c r="C91" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D91" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.25">
@@ -2625,10 +2625,10 @@
         <v>183</v>
       </c>
       <c r="C92" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D92" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.25">
@@ -2636,693 +2636,693 @@
         <v>184</v>
       </c>
       <c r="B93" t="s">
-        <v>185</v>
+        <v>307</v>
       </c>
       <c r="C93" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D93" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
+        <v>185</v>
+      </c>
+      <c r="B94" t="s">
         <v>186</v>
       </c>
-      <c r="B94" t="s">
-        <v>187</v>
-      </c>
       <c r="C94" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D94" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
+        <v>187</v>
+      </c>
+      <c r="B95" t="s">
         <v>188</v>
       </c>
-      <c r="B95" t="s">
-        <v>189</v>
-      </c>
       <c r="C95" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D95" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
+        <v>189</v>
+      </c>
+      <c r="B96" t="s">
         <v>190</v>
       </c>
-      <c r="B96" t="s">
-        <v>191</v>
-      </c>
       <c r="C96" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D96" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
+        <v>191</v>
+      </c>
+      <c r="B97" t="s">
         <v>192</v>
       </c>
-      <c r="B97" t="s">
-        <v>193</v>
-      </c>
       <c r="C97" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D97" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
+        <v>193</v>
+      </c>
+      <c r="B98" t="s">
         <v>194</v>
       </c>
-      <c r="B98" t="s">
-        <v>195</v>
-      </c>
       <c r="C98" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D98" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
+        <v>195</v>
+      </c>
+      <c r="B99" t="s">
         <v>196</v>
       </c>
-      <c r="B99" t="s">
-        <v>197</v>
-      </c>
       <c r="C99" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D99" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
+        <v>197</v>
+      </c>
+      <c r="B100" t="s">
         <v>198</v>
       </c>
-      <c r="B100" t="s">
-        <v>199</v>
-      </c>
       <c r="C100" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D100" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
+        <v>199</v>
+      </c>
+      <c r="B101" t="s">
         <v>200</v>
       </c>
-      <c r="B101" t="s">
-        <v>201</v>
-      </c>
       <c r="C101" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D101" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
+        <v>201</v>
+      </c>
+      <c r="B102" t="s">
         <v>202</v>
       </c>
-      <c r="B102" t="s">
-        <v>203</v>
-      </c>
       <c r="C102" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D102" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
+        <v>203</v>
+      </c>
+      <c r="B103" t="s">
         <v>204</v>
       </c>
-      <c r="B103" t="s">
-        <v>205</v>
-      </c>
       <c r="C103" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D103" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
+        <v>205</v>
+      </c>
+      <c r="B104" t="s">
         <v>206</v>
       </c>
-      <c r="B104" t="s">
-        <v>207</v>
-      </c>
       <c r="C104" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D104" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
+        <v>207</v>
+      </c>
+      <c r="B105" t="s">
         <v>208</v>
       </c>
-      <c r="B105" t="s">
-        <v>209</v>
-      </c>
       <c r="C105" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D105" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
+        <v>209</v>
+      </c>
+      <c r="B106" t="s">
         <v>210</v>
       </c>
-      <c r="B106" t="s">
-        <v>211</v>
-      </c>
       <c r="C106" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D106" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
+        <v>211</v>
+      </c>
+      <c r="B107" t="s">
         <v>212</v>
       </c>
-      <c r="B107" t="s">
-        <v>213</v>
-      </c>
       <c r="C107" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D107" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
+        <v>213</v>
+      </c>
+      <c r="B108" t="s">
         <v>214</v>
       </c>
-      <c r="B108" t="s">
-        <v>215</v>
-      </c>
       <c r="C108" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D108" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
+        <v>215</v>
+      </c>
+      <c r="B109" t="s">
         <v>216</v>
       </c>
-      <c r="B109" t="s">
-        <v>217</v>
-      </c>
       <c r="C109" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D109" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
+        <v>217</v>
+      </c>
+      <c r="B110" t="s">
         <v>218</v>
       </c>
-      <c r="B110" t="s">
-        <v>219</v>
-      </c>
       <c r="C110" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D110" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
+        <v>219</v>
+      </c>
+      <c r="B111" t="s">
         <v>220</v>
       </c>
-      <c r="B111" t="s">
-        <v>221</v>
-      </c>
       <c r="C111" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D111" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
+        <v>221</v>
+      </c>
+      <c r="B112" t="s">
         <v>222</v>
       </c>
-      <c r="B112" t="s">
-        <v>223</v>
-      </c>
       <c r="C112" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D112" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
+        <v>223</v>
+      </c>
+      <c r="B113" t="s">
         <v>224</v>
       </c>
-      <c r="B113" t="s">
-        <v>225</v>
-      </c>
       <c r="C113" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D113" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
+        <v>225</v>
+      </c>
+      <c r="B114" t="s">
         <v>226</v>
       </c>
-      <c r="B114" t="s">
-        <v>227</v>
-      </c>
       <c r="C114" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D114" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
+        <v>227</v>
+      </c>
+      <c r="B115" t="s">
         <v>228</v>
       </c>
-      <c r="B115" t="s">
-        <v>229</v>
-      </c>
       <c r="C115" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D115" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
+        <v>229</v>
+      </c>
+      <c r="B116" t="s">
         <v>230</v>
       </c>
-      <c r="B116" t="s">
-        <v>231</v>
-      </c>
       <c r="C116" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D116" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
+        <v>231</v>
+      </c>
+      <c r="B117" t="s">
         <v>232</v>
       </c>
-      <c r="B117" t="s">
-        <v>233</v>
-      </c>
       <c r="C117" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D117" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
+        <v>233</v>
+      </c>
+      <c r="B118" t="s">
         <v>234</v>
       </c>
-      <c r="B118" t="s">
-        <v>235</v>
-      </c>
       <c r="C118" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D118" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
+        <v>235</v>
+      </c>
+      <c r="B119" t="s">
         <v>236</v>
       </c>
-      <c r="B119" t="s">
-        <v>237</v>
-      </c>
       <c r="C119" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D119" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
+        <v>237</v>
+      </c>
+      <c r="B120" t="s">
         <v>238</v>
       </c>
-      <c r="B120" t="s">
-        <v>239</v>
-      </c>
       <c r="C120" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D120" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
+        <v>239</v>
+      </c>
+      <c r="B121" t="s">
         <v>240</v>
       </c>
-      <c r="B121" t="s">
-        <v>241</v>
-      </c>
       <c r="C121" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D121" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
+        <v>241</v>
+      </c>
+      <c r="B122" t="s">
         <v>242</v>
       </c>
-      <c r="B122" t="s">
-        <v>243</v>
-      </c>
       <c r="C122" t="s">
+        <v>270</v>
+      </c>
+      <c r="D122" t="s">
         <v>271</v>
-      </c>
-      <c r="D122" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
+        <v>243</v>
+      </c>
+      <c r="B123" t="s">
         <v>244</v>
       </c>
-      <c r="B123" t="s">
-        <v>245</v>
-      </c>
       <c r="C123" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D123" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
+        <v>245</v>
+      </c>
+      <c r="B124" t="s">
         <v>246</v>
       </c>
-      <c r="B124" t="s">
-        <v>247</v>
-      </c>
       <c r="C124" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D124" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
+        <v>247</v>
+      </c>
+      <c r="B125" t="s">
         <v>248</v>
       </c>
-      <c r="B125" t="s">
-        <v>249</v>
-      </c>
       <c r="C125" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D125" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
+        <v>249</v>
+      </c>
+      <c r="B126" t="s">
         <v>250</v>
       </c>
-      <c r="B126" t="s">
-        <v>251</v>
-      </c>
       <c r="C126" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D126" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
+        <v>251</v>
+      </c>
+      <c r="B127" t="s">
         <v>252</v>
       </c>
-      <c r="B127" t="s">
-        <v>253</v>
-      </c>
       <c r="C127" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D127" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
+        <v>253</v>
+      </c>
+      <c r="B128" t="s">
         <v>254</v>
       </c>
-      <c r="B128" t="s">
-        <v>255</v>
-      </c>
       <c r="C128" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="D128" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
+        <v>255</v>
+      </c>
+      <c r="B129" t="s">
         <v>256</v>
       </c>
-      <c r="B129" t="s">
-        <v>257</v>
-      </c>
       <c r="C129" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D129" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
+        <v>290</v>
+      </c>
+      <c r="B130" t="s">
         <v>291</v>
       </c>
-      <c r="B130" t="s">
-        <v>292</v>
-      </c>
       <c r="C130" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D130" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
+        <v>292</v>
+      </c>
+      <c r="B131" t="s">
         <v>293</v>
       </c>
-      <c r="B131" t="s">
-        <v>294</v>
-      </c>
       <c r="C131" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D131" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
+        <v>294</v>
+      </c>
+      <c r="B132" t="s">
         <v>295</v>
       </c>
-      <c r="B132" t="s">
-        <v>296</v>
-      </c>
       <c r="C132" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D132" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
+        <v>296</v>
+      </c>
+      <c r="B133" t="s">
         <v>297</v>
       </c>
-      <c r="B133" t="s">
-        <v>298</v>
-      </c>
       <c r="C133" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D133" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
+        <v>298</v>
+      </c>
+      <c r="B134" t="s">
         <v>299</v>
       </c>
-      <c r="B134" t="s">
-        <v>300</v>
-      </c>
       <c r="C134" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D134" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
+        <v>300</v>
+      </c>
+      <c r="B135" t="s">
         <v>301</v>
       </c>
-      <c r="B135" t="s">
-        <v>302</v>
-      </c>
       <c r="C135" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D135" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
+        <v>302</v>
+      </c>
+      <c r="B136" t="s">
         <v>303</v>
       </c>
-      <c r="B136" t="s">
-        <v>304</v>
-      </c>
       <c r="C136" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D136" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
+        <v>304</v>
+      </c>
+      <c r="B137" t="s">
         <v>305</v>
       </c>
-      <c r="B137" t="s">
-        <v>306</v>
-      </c>
       <c r="C137" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D137" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C138" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D138" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C139" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D139" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C140" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D140" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C141" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D141" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C142" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D142" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C143" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D143" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C144" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D144" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="145" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C145" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D145" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
   </sheetData>

--- a/bnc-streamlit-app/data/playerlist.xlsx
+++ b/bnc-streamlit-app/data/playerlist.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wt_an\WT Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3290730C-F02D-48E3-9960-72C2D6FB4115}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C1B0182-9791-46EA-8889-68ACA4686C64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F99C2274-98D2-4399-9250-8E7A0D0DACF8}"/>
+    <workbookView xWindow="2205" yWindow="2205" windowWidth="21600" windowHeight="11295" xr2:uid="{F99C2274-98D2-4399-9250-8E7A0D0DACF8}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="564" uniqueCount="308">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="580" uniqueCount="323">
   <si>
     <t>Player</t>
   </si>
@@ -905,9 +905,6 @@
     <t>Ivory Coast</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>BnC Position</t>
   </si>
   <si>
@@ -963,6 +960,54 @@
   </si>
   <si>
     <t>dodddfi0l5i36vlgbaybhzeqy</t>
+  </si>
+  <si>
+    <t>A. Gordon</t>
+  </si>
+  <si>
+    <t>8mjj0wgufggpc1ai2dk21h90p</t>
+  </si>
+  <si>
+    <t>Álex Baena</t>
+  </si>
+  <si>
+    <t>5zoz3mjooujpv0wdcphyrztd6</t>
+  </si>
+  <si>
+    <t>L. Digne</t>
+  </si>
+  <si>
+    <t>e8gz0tmmdh1ql8qrn1ncrvnpx</t>
+  </si>
+  <si>
+    <t>K. Ajer</t>
+  </si>
+  <si>
+    <t>32bvxwhceid2xdcfx6cd8a8d1</t>
+  </si>
+  <si>
+    <t>I. Saibari</t>
+  </si>
+  <si>
+    <t>9vf02r3geinhsy732oxyrcacq</t>
+  </si>
+  <si>
+    <t>A. Rabiot</t>
+  </si>
+  <si>
+    <t>2nddcty9qris2mmeldon0ogd1</t>
+  </si>
+  <si>
+    <t>N. Madueke</t>
+  </si>
+  <si>
+    <t>e3il1t1s5lrn4g8t85fcm40oa</t>
+  </si>
+  <si>
+    <t>Mikel Merino</t>
+  </si>
+  <si>
+    <t>atigcsq78g14w82lwvay26aj9</t>
   </si>
 </sst>
 </file>
@@ -1354,7 +1399,7 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -2510,7 +2555,7 @@
         <v>167</v>
       </c>
       <c r="B84" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C84" t="s">
         <v>282</v>
@@ -2636,7 +2681,7 @@
         <v>184</v>
       </c>
       <c r="B93" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C93" t="s">
         <v>273</v>
@@ -3151,10 +3196,10 @@
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
+        <v>289</v>
+      </c>
+      <c r="B130" t="s">
         <v>290</v>
-      </c>
-      <c r="B130" t="s">
-        <v>291</v>
       </c>
       <c r="C130" t="s">
         <v>264</v>
@@ -3165,10 +3210,10 @@
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
+        <v>291</v>
+      </c>
+      <c r="B131" t="s">
         <v>292</v>
-      </c>
-      <c r="B131" t="s">
-        <v>293</v>
       </c>
       <c r="C131" t="s">
         <v>264</v>
@@ -3179,10 +3224,10 @@
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
+        <v>293</v>
+      </c>
+      <c r="B132" t="s">
         <v>294</v>
-      </c>
-      <c r="B132" t="s">
-        <v>295</v>
       </c>
       <c r="C132" t="s">
         <v>280</v>
@@ -3193,10 +3238,10 @@
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
+        <v>295</v>
+      </c>
+      <c r="B133" t="s">
         <v>296</v>
-      </c>
-      <c r="B133" t="s">
-        <v>297</v>
       </c>
       <c r="C133" t="s">
         <v>274</v>
@@ -3207,10 +3252,10 @@
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
+        <v>297</v>
+      </c>
+      <c r="B134" t="s">
         <v>298</v>
-      </c>
-      <c r="B134" t="s">
-        <v>299</v>
       </c>
       <c r="C134" t="s">
         <v>273</v>
@@ -3221,10 +3266,10 @@
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
+        <v>299</v>
+      </c>
+      <c r="B135" t="s">
         <v>300</v>
-      </c>
-      <c r="B135" t="s">
-        <v>301</v>
       </c>
       <c r="C135" t="s">
         <v>261</v>
@@ -3235,10 +3280,10 @@
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
+        <v>301</v>
+      </c>
+      <c r="B136" t="s">
         <v>302</v>
-      </c>
-      <c r="B136" t="s">
-        <v>303</v>
       </c>
       <c r="C136" t="s">
         <v>280</v>
@@ -3249,10 +3294,10 @@
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
+        <v>303</v>
+      </c>
+      <c r="B137" t="s">
         <v>304</v>
-      </c>
-      <c r="B137" t="s">
-        <v>305</v>
       </c>
       <c r="C137" t="s">
         <v>261</v>
@@ -3262,67 +3307,115 @@
       </c>
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>307</v>
+      </c>
+      <c r="B138" t="s">
+        <v>308</v>
+      </c>
       <c r="C138" t="s">
-        <v>288</v>
+        <v>259</v>
       </c>
       <c r="D138" t="s">
-        <v>288</v>
+        <v>258</v>
       </c>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>309</v>
+      </c>
+      <c r="B139" t="s">
+        <v>310</v>
+      </c>
       <c r="C139" t="s">
-        <v>288</v>
+        <v>260</v>
       </c>
       <c r="D139" t="s">
-        <v>288</v>
+        <v>263</v>
       </c>
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>311</v>
+      </c>
+      <c r="B140" t="s">
+        <v>312</v>
+      </c>
       <c r="C140" t="s">
-        <v>288</v>
+        <v>257</v>
       </c>
       <c r="D140" t="s">
-        <v>288</v>
+        <v>268</v>
       </c>
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>313</v>
+      </c>
+      <c r="B141" t="s">
+        <v>314</v>
+      </c>
       <c r="C141" t="s">
-        <v>288</v>
+        <v>266</v>
       </c>
       <c r="D141" t="s">
-        <v>288</v>
+        <v>268</v>
       </c>
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>315</v>
+      </c>
+      <c r="B142" t="s">
+        <v>316</v>
+      </c>
       <c r="C142" t="s">
-        <v>288</v>
+        <v>270</v>
       </c>
       <c r="D142" t="s">
-        <v>288</v>
+        <v>263</v>
       </c>
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>317</v>
+      </c>
+      <c r="B143" t="s">
+        <v>318</v>
+      </c>
       <c r="C143" t="s">
-        <v>288</v>
+        <v>257</v>
       </c>
       <c r="D143" t="s">
-        <v>288</v>
+        <v>263</v>
       </c>
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>319</v>
+      </c>
+      <c r="B144" t="s">
+        <v>320</v>
+      </c>
       <c r="C144" t="s">
-        <v>288</v>
+        <v>259</v>
       </c>
       <c r="D144" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="145" spans="3:4" x14ac:dyDescent="0.25">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>321</v>
+      </c>
+      <c r="B145" t="s">
+        <v>322</v>
+      </c>
       <c r="C145" t="s">
-        <v>288</v>
+        <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>288</v>
+        <v>263</v>
       </c>
     </row>
   </sheetData>
